--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261019.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261019.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>22,258</t>
+          <t>95,863</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>95,863</t>
+          <t>22,258</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>51,610</t>
+          <t>27,669</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>27,669</t>
+          <t>51,610</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
